--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-seizure-record</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-seizure-record</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3862,7 +3854,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3880,23 +3872,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3923,10 +3915,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3934,13 +3926,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -3984,7 +3976,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -4002,10 +3994,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -4047,10 +4039,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4058,14 +4050,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4087,16 +4079,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4106,29 +4098,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4145,7 +4137,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4160,30 +4152,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4206,19 +4198,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4267,7 +4259,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4282,19 +4274,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4302,10 +4294,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4328,16 +4320,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4387,7 +4379,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4408,13 +4400,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4422,14 +4414,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4448,19 +4440,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4509,7 +4501,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4524,19 +4516,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4544,14 +4536,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4570,19 +4562,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4631,7 +4623,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4646,19 +4638,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4666,10 +4658,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4692,16 +4684,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4751,7 +4743,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4772,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4786,10 +4778,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4812,17 +4804,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4871,7 +4863,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4886,19 +4878,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4906,10 +4898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4932,19 +4924,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4993,7 +4985,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5002,7 +4994,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5011,27 +5003,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5057,16 +5049,16 @@
         <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -5091,14 +5083,14 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
       </c>
@@ -5115,7 +5107,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5124,7 +5116,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -5139,7 +5131,7 @@
         <v>133</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -5150,14 +5142,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5179,16 +5171,16 @@
         <v>188</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -5213,14 +5205,14 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
@@ -5237,7 +5229,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5255,27 +5247,27 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5298,19 +5290,19 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5359,7 +5351,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5380,10 +5372,10 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5394,10 +5386,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5423,13 +5415,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5455,14 +5447,14 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5479,7 +5471,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5497,27 +5489,27 @@
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5543,16 +5535,16 @@
         <v>188</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5577,14 +5569,14 @@
         <v>18</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5601,7 +5593,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5622,10 +5614,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5636,10 +5628,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5662,16 +5654,16 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5721,7 +5713,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5739,27 +5731,27 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5782,16 +5774,16 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5841,7 +5833,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5859,27 +5851,27 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5902,19 +5894,19 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5963,7 +5955,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5975,19 +5967,19 @@
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -5998,10 +5990,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6024,13 +6016,13 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6081,7 +6073,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6105,7 +6097,7 @@
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -6116,10 +6108,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6148,7 +6140,7 @@
         <v>137</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -6201,7 +6193,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6225,7 +6217,7 @@
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6236,14 +6228,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6265,10 +6257,10 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>139</v>
@@ -6323,7 +6315,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6358,10 +6350,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6384,13 +6376,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6441,7 +6433,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6450,7 +6442,7 @@
         <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
@@ -6462,10 +6454,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6476,10 +6468,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6502,13 +6494,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6559,7 +6551,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6568,7 +6560,7 @@
         <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>102</v>
@@ -6580,10 +6572,10 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6594,10 +6586,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6623,16 +6615,16 @@
         <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6660,11 +6652,11 @@
         <v>114</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6681,7 +6673,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6699,13 +6691,13 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>18</v>
@@ -6716,10 +6708,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6745,16 +6737,16 @@
         <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6779,14 +6771,14 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
       </c>
@@ -6803,7 +6795,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6821,13 +6813,13 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6838,10 +6830,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6864,17 +6856,17 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6923,7 +6915,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6947,7 +6939,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -6958,10 +6950,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6984,13 +6976,13 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7041,7 +7033,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7062,10 +7054,10 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7076,10 +7068,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7102,16 +7094,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7161,7 +7153,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7182,10 +7174,10 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -7196,10 +7188,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7222,16 +7214,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7281,7 +7273,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7302,10 +7294,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7316,10 +7308,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7342,19 +7334,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7391,17 +7383,17 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7422,10 +7414,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7436,10 +7428,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7462,13 +7454,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7519,7 +7511,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7543,7 +7535,7 @@
         <v>18</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7554,10 +7546,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7586,7 +7578,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7639,7 +7631,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7663,7 +7655,7 @@
         <v>18</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7674,14 +7666,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7703,10 +7695,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7761,7 +7753,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7796,10 +7788,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7825,16 +7817,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7859,14 +7851,14 @@
         <v>18</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7883,7 +7875,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7901,16 +7893,16 @@
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>18</v>
@@ -7918,10 +7910,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7944,19 +7936,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -8005,7 +7997,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8023,27 +8015,27 @@
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8069,16 +8061,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -8103,14 +8095,14 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8127,7 +8119,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8136,7 +8128,7 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -8151,7 +8143,7 @@
         <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8162,14 +8154,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8191,16 +8183,16 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8225,14 +8217,14 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
       </c>
@@ -8249,7 +8241,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8267,27 +8259,27 @@
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8313,16 +8305,16 @@
         <v>80</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8371,7 +8363,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8392,10 +8384,10 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8406,13 +8398,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>18</v>
@@ -8434,19 +8426,19 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8495,7 +8487,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8516,10 +8508,10 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8530,10 +8522,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8556,13 +8548,13 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8613,7 +8605,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8637,7 +8629,7 @@
         <v>18</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
@@ -8648,10 +8640,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8680,7 +8672,7 @@
         <v>137</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8733,7 +8725,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8757,7 +8749,7 @@
         <v>18</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
@@ -8768,14 +8760,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8797,10 +8789,10 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>139</v>
@@ -8855,7 +8847,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8890,10 +8882,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8919,16 +8911,16 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8938,7 +8930,7 @@
         <v>18</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>18</v>
@@ -8953,14 +8945,14 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8977,7 +8969,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>90</v>
@@ -8995,16 +8987,16 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>18</v>
@@ -9012,10 +9004,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9038,19 +9030,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O58" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9099,7 +9091,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9117,27 +9109,27 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9163,16 +9155,16 @@
         <v>188</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9197,14 +9189,14 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>18</v>
       </c>
@@ -9221,7 +9213,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9230,7 +9222,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -9245,7 +9237,7 @@
         <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9256,14 +9248,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9285,16 +9277,16 @@
         <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9319,14 +9311,14 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9343,7 +9335,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9361,27 +9353,27 @@
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9407,16 +9399,16 @@
         <v>80</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N61" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>18</v>
@@ -9465,7 +9457,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9486,10 +9478,10 @@
         <v>18</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9500,13 +9492,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>18</v>
@@ -9528,19 +9520,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>18</v>
@@ -9589,7 +9581,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9610,10 +9602,10 @@
         <v>18</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9624,10 +9616,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9650,13 +9642,13 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9707,7 +9699,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9731,7 +9723,7 @@
         <v>18</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
@@ -9742,10 +9734,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9774,7 +9766,7 @@
         <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>139</v>
@@ -9827,7 +9819,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9851,7 +9843,7 @@
         <v>18</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>18</v>
@@ -9862,14 +9854,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9891,10 +9883,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>139</v>
@@ -9949,7 +9941,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9984,10 +9976,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10013,16 +10005,16 @@
         <v>188</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N66" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O66" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -10032,7 +10024,7 @@
         <v>18</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>18</v>
@@ -10047,14 +10039,14 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y66" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Z66" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
       </c>
@@ -10071,7 +10063,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>90</v>
@@ -10089,16 +10081,16 @@
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>18</v>
@@ -10106,10 +10098,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10132,19 +10124,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10193,7 +10185,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10211,27 +10203,27 @@
         <v>18</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10254,13 +10246,13 @@
         <v>18</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10311,7 +10303,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10335,7 +10327,7 @@
         <v>18</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>18</v>
@@ -10346,10 +10338,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10378,7 +10370,7 @@
         <v>137</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>139</v>
@@ -10419,19 +10411,19 @@
         <v>18</v>
       </c>
       <c r="AB69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AC69" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AC69" t="s" s="2">
-        <v>478</v>
-      </c>
       <c r="AD69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10455,7 +10447,7 @@
         <v>18</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10466,10 +10458,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10492,19 +10484,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -10553,7 +10545,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10574,10 +10566,10 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10588,10 +10580,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10617,20 +10609,20 @@
         <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q71" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q71" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="R71" t="s" s="2">
         <v>18</v>
@@ -10654,28 +10646,28 @@
         <v>179</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10696,10 +10688,10 @@
         <v>18</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10710,10 +10702,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10736,17 +10728,17 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>18</v>
@@ -10756,46 +10748,46 @@
         <v>18</v>
       </c>
       <c r="S72" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10816,10 +10808,10 @@
         <v>18</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>18</v>
@@ -10830,10 +10822,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10859,14 +10851,14 @@
         <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>18</v>
@@ -10876,46 +10868,46 @@
         <v>18</v>
       </c>
       <c r="S73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10924,7 +10916,7 @@
         <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>102</v>
@@ -10936,10 +10928,10 @@
         <v>18</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>18</v>
@@ -10950,10 +10942,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10979,16 +10971,16 @@
         <v>110</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -10998,7 +10990,7 @@
         <v>18</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>18</v>
@@ -11037,7 +11029,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11058,10 +11050,10 @@
         <v>18</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>18</v>
@@ -11072,10 +11064,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11101,16 +11093,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -11135,14 +11127,14 @@
         <v>18</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y75" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Z75" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>18</v>
       </c>
@@ -11159,7 +11151,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11168,7 +11160,7 @@
         <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>102</v>
@@ -11183,7 +11175,7 @@
         <v>133</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>18</v>
@@ -11194,14 +11186,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11223,16 +11215,16 @@
         <v>188</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -11257,14 +11249,14 @@
         <v>18</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>18</v>
       </c>
@@ -11281,7 +11273,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11299,27 +11291,27 @@
         <v>18</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11345,16 +11337,16 @@
         <v>80</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N77" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
@@ -11403,7 +11395,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11424,10 +11416,10 @@
         <v>18</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
@@ -11438,13 +11430,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>18</v>
@@ -11466,19 +11458,19 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>18</v>
@@ -11527,7 +11519,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11548,10 +11540,10 @@
         <v>18</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>18</v>
@@ -11562,10 +11554,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11588,13 +11580,13 @@
         <v>18</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11645,7 +11637,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11669,7 +11661,7 @@
         <v>18</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11680,10 +11672,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11712,7 +11704,7 @@
         <v>137</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>139</v>
@@ -11765,7 +11757,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11789,7 +11781,7 @@
         <v>18</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>18</v>
@@ -11800,14 +11792,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11829,10 +11821,10 @@
         <v>136</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>139</v>
@@ -11887,7 +11879,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11922,10 +11914,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11951,16 +11943,16 @@
         <v>188</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N82" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O82" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>18</v>
@@ -11970,7 +11962,7 @@
         <v>18</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>18</v>
@@ -11985,14 +11977,14 @@
         <v>18</v>
       </c>
       <c r="X82" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y82" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y82" t="s" s="2">
+      <c r="Z82" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>18</v>
       </c>
@@ -12009,7 +12001,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12027,16 +12019,16 @@
         <v>18</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>18</v>
@@ -12044,10 +12036,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12070,19 +12062,19 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O83" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>18</v>
@@ -12131,7 +12123,7 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12149,27 +12141,27 @@
         <v>18</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12195,16 +12187,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12229,14 +12221,14 @@
         <v>18</v>
       </c>
       <c r="X84" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y84" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Z84" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>18</v>
       </c>
@@ -12253,7 +12245,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12262,7 +12254,7 @@
         <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>102</v>
@@ -12277,7 +12269,7 @@
         <v>133</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>18</v>
@@ -12288,14 +12280,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12317,16 +12309,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>18</v>
@@ -12351,14 +12343,14 @@
         <v>18</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>18</v>
       </c>
@@ -12375,7 +12367,7 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12393,27 +12385,27 @@
         <v>18</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12439,16 +12431,16 @@
         <v>80</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N86" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -12497,7 +12489,7 @@
         <v>18</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12518,10 +12510,10 @@
         <v>18</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>18</v>
@@ -12532,13 +12524,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>18</v>
@@ -12560,19 +12552,19 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>18</v>
@@ -12621,7 +12613,7 @@
         <v>18</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12642,10 +12634,10 @@
         <v>18</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>18</v>
@@ -12656,10 +12648,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12682,13 +12674,13 @@
         <v>18</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12739,7 +12731,7 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12763,7 +12755,7 @@
         <v>18</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>18</v>
@@ -12774,10 +12766,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12806,7 +12798,7 @@
         <v>137</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>139</v>
@@ -12859,7 +12851,7 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12883,7 +12875,7 @@
         <v>18</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>18</v>
@@ -12894,14 +12886,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12923,10 +12915,10 @@
         <v>136</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>139</v>
@@ -12981,7 +12973,7 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13016,10 +13008,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13045,16 +13037,16 @@
         <v>188</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N91" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>18</v>
@@ -13064,7 +13056,7 @@
         <v>18</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>18</v>
@@ -13079,14 +13071,14 @@
         <v>18</v>
       </c>
       <c r="X91" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y91" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y91" t="s" s="2">
+      <c r="Z91" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>18</v>
       </c>
@@ -13103,7 +13095,7 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>90</v>
@@ -13121,16 +13113,16 @@
         <v>18</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>18</v>
@@ -13138,10 +13130,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13164,19 +13156,19 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>18</v>
@@ -13225,7 +13217,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13243,27 +13235,27 @@
         <v>18</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13289,16 +13281,16 @@
         <v>188</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="N93" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>18</v>
@@ -13323,14 +13315,14 @@
         <v>18</v>
       </c>
       <c r="X93" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y93" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y93" t="s" s="2">
+      <c r="Z93" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>18</v>
       </c>
@@ -13347,7 +13339,7 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13356,7 +13348,7 @@
         <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>102</v>
@@ -13371,7 +13363,7 @@
         <v>133</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>18</v>
@@ -13382,14 +13374,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13411,16 +13403,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>18</v>
@@ -13445,14 +13437,14 @@
         <v>18</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>18</v>
       </c>
@@ -13469,7 +13461,7 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13487,27 +13479,27 @@
         <v>18</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13533,16 +13525,16 @@
         <v>80</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N95" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>18</v>
@@ -13591,7 +13583,7 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13612,10 +13604,10 @@
         <v>18</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-seizure-record.xlsx
+++ b/StructureDefinition-onc-seizure-record.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
